--- a/results/0916-all/粤西桂南农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/粤西桂南农林区/tech_selected_summary.xlsx
@@ -217,274 +217,274 @@
     <t>长洲区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>技术82</t>
-  </si>
-  <si>
-    <t>技术83</t>
-  </si>
-  <si>
-    <t>技术84</t>
-  </si>
-  <si>
-    <t>技术85</t>
-  </si>
-  <si>
-    <t>技术86</t>
-  </si>
-  <si>
-    <t>技术87</t>
-  </si>
-  <si>
-    <t>技术88</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Tech82</t>
+  </si>
+  <si>
+    <t>Tech83</t>
+  </si>
+  <si>
+    <t>Tech84</t>
+  </si>
+  <si>
+    <t>Tech85</t>
+  </si>
+  <si>
+    <t>Tech86</t>
+  </si>
+  <si>
+    <t>Tech87</t>
+  </si>
+  <si>
+    <t>Tech88</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -547,7 +547,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 297419220.72</t>
+    <t>297419220.72</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -619,7 +619,7 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 1054613230.74</t>
+    <t>1054613230.74</t>
   </si>
   <si>
     <t>Yucca extract_sheep &amp; goat</t>
@@ -652,22 +652,22 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 885538862.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 3807608.45</t>
+    <t>885538862.68</t>
+  </si>
+  <si>
+    <t>3807608.45</t>
   </si>
   <si>
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 72740326.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 1641771.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>72740326.80</t>
+  </si>
+  <si>
+    <t>1641771.58</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -745,7 +745,7 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 1389302509.93</t>
+    <t>1389302509.93</t>
   </si>
   <si>
     <t>Screw press_pig</t>
@@ -763,25 +763,25 @@
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 250848285.03</t>
-  </si>
-  <si>
-    <t>总经济成本: 1011376.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 24786214.15</t>
+    <t>250848285.03</t>
+  </si>
+  <si>
+    <t>1011376.68</t>
+  </si>
+  <si>
+    <t>24786214.15</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 421153335.54</t>
+    <t>421153335.54</t>
   </si>
   <si>
     <t>Chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 377229494.70</t>
+    <t>377229494.70</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -814,13 +814,13 @@
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 2172203870.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 163519864.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 218193732.23</t>
+    <t>2172203870.91</t>
+  </si>
+  <si>
+    <t>163519864.62</t>
+  </si>
+  <si>
+    <t>218193732.23</t>
   </si>
   <si>
     <t>Biochar_dairy</t>
@@ -841,7 +841,7 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 688410798.94</t>
+    <t>688410798.94</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -892,19 +892,19 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 2317104495.14</t>
-  </si>
-  <si>
-    <t>总经济成本: 102251458.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 141634796.94</t>
-  </si>
-  <si>
-    <t>总经济成本: 621013.22</t>
-  </si>
-  <si>
-    <t>总经济成本: 6818913.43</t>
+    <t>2317104495.14</t>
+  </si>
+  <si>
+    <t>102251458.52</t>
+  </si>
+  <si>
+    <t>141634796.94</t>
+  </si>
+  <si>
+    <t>621013.22</t>
+  </si>
+  <si>
+    <t>6818913.43</t>
   </si>
   <si>
     <t>compost（high）≥70%_friut</t>
@@ -931,88 +931,88 @@
     <t>irrigation (water-saving irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 916503845.40</t>
+    <t>916503845.40</t>
   </si>
   <si>
     <t>sulfate_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 1462074789.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 671567.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 323052585.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 441616869.10</t>
+    <t>1462074789.65</t>
+  </si>
+  <si>
+    <t>671567.72</t>
+  </si>
+  <si>
+    <t>323052585.60</t>
+  </si>
+  <si>
+    <t>441616869.10</t>
   </si>
   <si>
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 821672524.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 7190219.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 1471316.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 300977264.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 1824529.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 214392027.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 2156535267.03</t>
+    <t>821672524.49</t>
+  </si>
+  <si>
+    <t>7190219.88</t>
+  </si>
+  <si>
+    <t>1471316.00</t>
+  </si>
+  <si>
+    <t>300977264.82</t>
+  </si>
+  <si>
+    <t>1824529.75</t>
+  </si>
+  <si>
+    <t>214392027.68</t>
+  </si>
+  <si>
+    <t>2156535267.03</t>
   </si>
   <si>
     <t>Urease Inhibitor_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 897800612.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 506427950.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 366470154.62</t>
-  </si>
-  <si>
-    <t>总经济成本: 699987.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 537265288.21</t>
-  </si>
-  <si>
-    <t>总经济成本: 3895802.88</t>
+    <t>897800612.72</t>
+  </si>
+  <si>
+    <t>506427950.21</t>
+  </si>
+  <si>
+    <t>366470154.62</t>
+  </si>
+  <si>
+    <t>699987.09</t>
+  </si>
+  <si>
+    <t>537265288.21</t>
+  </si>
+  <si>
+    <t>3895802.88</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 83180594.74</t>
-  </si>
-  <si>
-    <t>总经济成本: 2233398.23</t>
-  </si>
-  <si>
-    <t>总经济成本: 1352466.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 507759164.64</t>
-  </si>
-  <si>
-    <t>总经济成本: 448429813.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 308952606.43</t>
+    <t>83180594.74</t>
+  </si>
+  <si>
+    <t>2233398.23</t>
+  </si>
+  <si>
+    <t>1352466.13</t>
+  </si>
+  <si>
+    <t>507759164.64</t>
+  </si>
+  <si>
+    <t>448429813.97</t>
+  </si>
+  <si>
+    <t>308952606.43</t>
   </si>
   <si>
     <t>Bioflilter_pig</t>
@@ -1021,37 +1021,37 @@
     <t>Bioflilter_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 2156189278.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 105808020.77</t>
-  </si>
-  <si>
-    <t>总经济成本: 710945814.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 1095705014.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 355664726.98</t>
-  </si>
-  <si>
-    <t>总经济成本: -527909.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 417354052.55</t>
-  </si>
-  <si>
-    <t>总经济成本: 45433271.83</t>
+    <t>2156189278.73</t>
+  </si>
+  <si>
+    <t>105808020.77</t>
+  </si>
+  <si>
+    <t>710945814.91</t>
+  </si>
+  <si>
+    <t>1095705014.70</t>
+  </si>
+  <si>
+    <t>355664726.98</t>
+  </si>
+  <si>
+    <t>-527909.31</t>
+  </si>
+  <si>
+    <t>417354052.55</t>
+  </si>
+  <si>
+    <t>45433271.83</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 1403823512.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 86807833.13</t>
+    <t>1403823512.72</t>
+  </si>
+  <si>
+    <t>86807833.13</t>
   </si>
 </sst>
 </file>
